--- a/Blog.xlsx
+++ b/Blog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\austinz\Desktop\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F510DB-08D2-4EDD-9AEE-F8735FFEC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164E7A1-A8FA-4567-BB60-5A004AEAE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{275F5470-4899-460C-BFB9-CB0C30FDBC08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>pageTitle</t>
   </si>
@@ -66,6 +66,54 @@
   </si>
   <si>
     <t>https://www.danscomp.com/dans-comp-team-riders/cp1390</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/about_us/employees_thumbnail2.jpg</t>
+  </si>
+  <si>
+    <t>Discover the heart of Dan's Comp—a team fueled by unwavering BMX passion. From old-school pioneers to new-school innovators, our crew embodies the diverse spirit of BMX culture. Join us as we dive into the world where work and play seamlessly intertwine.</t>
+  </si>
+  <si>
+    <t>Meet The Dan's Comp Employees</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/meet-the-dans-comp-employees/cp1500</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/techhelp_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Tech Help</t>
+  </si>
+  <si>
+    <t>All of the technical details you can think of regarding BMX bikes. Dan's Comp has blog posts with details on how to install parts, make adjustments, how products work, and so much more.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/tech-help/cp1369</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_tricks/bmxtrickshowtos_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>BMX Trick How To's</t>
+  </si>
+  <si>
+    <t>We break down tricks and explain the how to learn each one step by step. Learn the details of each trick, where to learn them, and some pro tips on how to get them dialed. From simple skills such as jumping and manuals, to advance tricks like tailwhips, 360s and wallrides, Dan's Comp has these skills dissected to help you learn how to do them properly.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-trick-how-tos/cp1459</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/blog/bmx/buyers_guide/thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Shopping for a BMX bike may seem like a daunting task, but with a little help you’ll soon find that not only is it relatively easy, it’s one of the most enjoyable aspects of BMX riding. In this article we cover the basics of choosing your next bike based on several different factors including height, specs, and most importantly, what type of riding you want to do! From freestyle bikes, to race bikes and cruisers, we touch on it all.</t>
+  </si>
+  <si>
+    <t>BMX Bike Buyers Guide</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-bike-buyers-guide/cp1308</t>
   </si>
 </sst>
 </file>
@@ -458,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674831E4-6510-4789-AF71-D3A711C4CE6F}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
@@ -509,10 +557,92 @@
         <v>45161</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>1500</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>1369</v>
+      </c>
+      <c r="F4" s="2">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>1459</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45293</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>1308</v>
+      </c>
+      <c r="F6" s="2">
+        <v>44964</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{32DB9B8C-A366-4C6E-89D0-60B33590E24F}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{563B04B7-F378-49A3-B282-4E12C84BD449}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{94A9F92A-0AC6-4EDA-9CBA-F79A046DC061}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{02449328-A529-4F1A-B5BA-7DF01846F8EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Blog.xlsx
+++ b/Blog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\austinz\Desktop\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164E7A1-A8FA-4567-BB60-5A004AEAE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A05A778-9597-4A76-AD68-9F9A0B7F1612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{275F5470-4899-460C-BFB9-CB0C30FDBC08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>pageTitle</t>
   </si>
@@ -62,15 +62,9 @@
     <t>Meet the Dan's Comp team riders! Get to know our Pro and Flow team riders and see them shred!</t>
   </si>
   <si>
-    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/sites/danscomp/team_riders/teamriders2025_2.jpg</t>
-  </si>
-  <si>
     <t>https://www.danscomp.com/dans-comp-team-riders/cp1390</t>
   </si>
   <si>
-    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/about_us/employees_thumbnail2.jpg</t>
-  </si>
-  <si>
     <t>Discover the heart of Dan's Comp—a team fueled by unwavering BMX passion. From old-school pioneers to new-school innovators, our crew embodies the diverse spirit of BMX culture. Join us as we dive into the world where work and play seamlessly intertwine.</t>
   </si>
   <si>
@@ -80,9 +74,6 @@
     <t>https://www.danscomp.com/meet-the-dans-comp-employees/cp1500</t>
   </si>
   <si>
-    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/techhelp_thumbnail.jpg</t>
-  </si>
-  <si>
     <t>Tech Help</t>
   </si>
   <si>
@@ -92,9 +83,6 @@
     <t>https://www.danscomp.com/tech-help/cp1369</t>
   </si>
   <si>
-    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_tricks/bmxtrickshowtos_thumbnail.jpg</t>
-  </si>
-  <si>
     <t>BMX Trick How To's</t>
   </si>
   <si>
@@ -104,9 +92,6 @@
     <t>https://www.danscomp.com/bmx-trick-how-tos/cp1459</t>
   </si>
   <si>
-    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/blog/bmx/buyers_guide/thumbnail.jpg</t>
-  </si>
-  <si>
     <t>Shopping for a BMX bike may seem like a daunting task, but with a little help you’ll soon find that not only is it relatively easy, it’s one of the most enjoyable aspects of BMX riding. In this article we cover the basics of choosing your next bike based on several different factors including height, specs, and most importantly, what type of riding you want to do! From freestyle bikes, to race bikes and cruisers, we touch on it all.</t>
   </si>
   <si>
@@ -114,6 +99,249 @@
   </si>
   <si>
     <t>https://www.danscomp.com/bmx-bike-buyers-guide/cp1308</t>
+  </si>
+  <si>
+    <t>BMX Parts Guide: How to Upgrade and Replace Components</t>
+  </si>
+  <si>
+    <t>Upgrading your complete BMX bike is a fun way to personalize your ride—but with so many options, it can get confusing fast. This guide breaks down each component, covering sizing, compatibility, and upgrade tips. Start with budget-friendly parts and work your way to bigger upgrades. Use our interactive bike diagram or scroll through the list to learn how to confidently choose the best parts for your BMX.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-parts-guide-how-to-upgrade-and-replace-components/cp1673</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/images/sites/danscomp/team_riders/teamriders2025_2.jpg</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/images/contentpages/danscomp/about_us/employees_thumbnail2.jpg</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/images/contentpages/danscomp/tech_help/techhelp_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/images/contentpages/danscomp/how_to_tricks/bmxtrickshowtos_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/images/blog/bmx/buyers_guide/thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/images/contentpages/danscomp/tech_help/bike_anatomy/anatomy_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/2uOC8AkS84Q/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Best Entry Level Bikes: What to look for</t>
+  </si>
+  <si>
+    <t>Finding that perfect entry level bike can be difficult. Luckily, you don't have to spend a ton of money for something that's designed for real BMX use. The Verde Cadet represents exactly what you want in any beginner to mid level BMX bike. In this video we show you what a bike like the Cadet can really do, and why a department store bike just isn't up to snuff.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/best-entry-level-bikes-what-to-look-for/cp1185</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/complete_bike_upgrades/first/thumbnail1.jpg</t>
+  </si>
+  <si>
+    <t>First Upgrades To A Complete BMX Bike</t>
+  </si>
+  <si>
+    <t>Customizing your BMX bike is one of the most exciting parts of riding, allowing you to create a setup that reflects your personality. Many riders start with a complete bike and gradually swap out parts to make it their own. Whether you prefer bold colors and matching decals or a clean, minimalist style, personalization is key. In this guide, we cover the five most common parts riders upgrade to give their bike a unique look and feel that stands out on the streets or at the skatepark.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/first-upgrades-to-a-complete-bmx-bike/cp1596</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/VUfz0Rqhvic/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Best BMX Bike Upgrades</t>
+  </si>
+  <si>
+    <t>What are the best upgrades for your BMX bike? This is an important and common question we get from both new and seasoned riders. These parts can vary slightly from rider to rider and bike to bike, but we break down our top choices in order of importance. These changes can be essential to how your bike functions and performs.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/best-bmx-bike-upgrades/cp903</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/-EjB7XfB6fE/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>How do I build my new BMX bike?</t>
+  </si>
+  <si>
+    <t>Learn what all is needed to build your brand new bike up yourself! With a few simple hand tools and basic mechanical knowledge, you can build your new BMX right at home or even at the skatepark. From freestyle bikes to race bikes, this video will guide you through the process.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-do-i-build-my-new-bmx-bike/cp485</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/blog/bmx/cp1308/howtojumpthumbnail.jpg</t>
+  </si>
+  <si>
+    <t>How To Jump a BMX bike (Including MTB and DJ BIkes)</t>
+  </si>
+  <si>
+    <t>Jumping is an essential part of BMX that every rider should learn whether you ride street, trails, park or race. Because no matter the discipline, at some point your wheels will leave the ground and you need to make sure you have proper technique.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-jump-a-bmx-bike-including-mtb-and-dj-bikes/cp1362</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/ERBALEn56y0/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>BMX Frame Geometry</t>
+  </si>
+  <si>
+    <t>BMX frame geometry can seem rather complicated at first glance. With all the various sizes and angles listed, how do these changes in geometry affect your riding? We break down toptube length, headtube angle, bottom bracket height, and everything in-between, to help you choose that perfect frame based on your riding style.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-frame-geometry/cp907</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-frame-faqs/cp488</t>
+  </si>
+  <si>
+    <t>Upgrading the frame of your BMX bike is the biggest change you can make. This is a big deal because it is one of the more pricey upgrades, but also because there is so much that goes in to the decision. Frame geometry, material, sizing, compatible parts, and so on. Here, we take a deep dive on why upgrading to an aftermarket frame is a good decision and what all goes in to making that decision.</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/eUcL0uCGFGU/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>BMX Frame FAQ's</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/howto-tuck-no-hander-featuring-brady-baker/cp1819</t>
+  </si>
+  <si>
+    <t>Learn how to do a tuck no hander step-by-step with X-Games gold medalist Brady Baker. Learn to fly!</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/yi_QlPDaUKc/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>How-To Tuck No Hander | Featuring Brady Baker</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/40th-anniversary-about-us/cp1800</t>
+  </si>
+  <si>
+    <t>As Dan’s Comp celebrates 40 years in BMX, we’re spotlighting the people behind the scenes who help make it all happen. From lifelong riders to industry newcomers, meet the staff who grew up riding bikes, found their way into Dan’s Comp, and continue pushing BMX forward every day. This anniversary feature dives into their stories, roles, and shared passion that has fueled four decades—and counting.</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/sites/danscomp/home/2026/hero/40th_desk.jpg</t>
+  </si>
+  <si>
+    <t>40th Anniversary | About Us</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-chain-guide-sizes-styles-strength-explained/cp1715</t>
+  </si>
+  <si>
+    <t>Choosing the right BMX chain is key for performance and safety. This guide breaks down chain sizes (1/8" vs. 3/32"), styles (full link vs. half link), and strength ratings (410 vs. 510). Learn which chains are best for freestyle or race riding, why half links are the strongest option, and how a quality chain can prevent dangerous breakages.</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/chain_install.jpg</t>
+  </si>
+  <si>
+    <t>BMX Chain Guide: Sizes, Styles &amp; Strength Explained</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/what-to-know-when-buying-new-bmx-cranks/cp1711</t>
+  </si>
+  <si>
+    <t>Choosing the right BMX crankset can be confusing, but it doesn’t have to be. In this guide, we break down everything you need to know—from crank arm length and spindle diameter to spline types and drive side compatibility. Whether you're upgrading your freestyle setup or replacing worn-out parts, we’ll help you understand the options and pick the perfect crank for your ride. With visuals, side-by-side comparisons, and expert tips throughout, this article is your go-to resource for all things BMX</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/crank_sizing/measurement.png</t>
+  </si>
+  <si>
+    <t>What To Know When Buying New BMX Cranks</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-tire-sizes/cp1687</t>
+  </si>
+  <si>
+    <t>Explore BMX tire sizes and types with Dan's Comp's comprehensive guide. Learn the differences between freestyle and race BMX tires, understand ISO measurements, and find the perfect fit for your bike. Includes filter tips, tire installation help, and popular tire recommendations.</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/tires/tire_sizes_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>BMX Tire Sizes</t>
+  </si>
+  <si>
+    <t>Swamp Fest 2025</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/swampfest25/our_thumb.jpg</t>
+  </si>
+  <si>
+    <t>Check out all of the madness that went down on the Dan's Comp curved wallride of doom at Swamp Fest 2025! Shredding from legends like Gary Young and Dennis Enarson and young guns like Tyler Hill. MVP certainly went to our homie Jake Rutkowitz for some bangers, including a flip out!</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/swamp-fest-2025/cp1662</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bloom-bmx-x-woodward-giveaway/cp1612</t>
+  </si>
+  <si>
+    <t>Dan's Comp is honoring International Women's Day by pairing up with the amazing ladies at Bloom BMX to send one women to Camp Woodward during their 'Ride Like a Girl' weekend! This isn't a normal contest. Bloom BMX is having people nominate women they think deserve this opportunity. To learn more and to nominate a lady you believe deserves this opportunity, visit the Bloom BMX Instagram page.</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/bloombmx_woodward/bloom_no_button.jpg</t>
+  </si>
+  <si>
+    <t>Bloom BMX X Woodward Giveaway</t>
+  </si>
+  <si>
+    <t>Send Your Wish List To Family &amp; Friends</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/holiday24/wishlist2024v2.png</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/send-your-wish-list-to-family-friends/cp1586</t>
+  </si>
+  <si>
+    <t>Don’t get stuck with lame gifts this year! Create your dream BMX wish list and send it to family/friends. Help grandma get you the right set of bars rather than some socks. Girlfriend wants a necklace? You want a freecoaster! Get exactly what you want and help your family by making shopping easy for them.</t>
+  </si>
+  <si>
+    <t>BMX Rear Hub Types</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/rear_hub.jpg</t>
+  </si>
+  <si>
+    <t>Explore our in-depth guide to BMX rear hubs, covering cassette, freecoaster, and freewheel types. Learn about clutch-based, planetary, switchable, and magnet-based freecoaster hubs with detailed pros, cons, and mechanics for each. Discover how BMX rear hubs work, their components, and find links to shop high-quality hubs at Dan's Comp.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-rear-hub-types/cp1572</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/gyro/gyro_thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Gyro? Detangler?</t>
+  </si>
+  <si>
+    <t>Detanglers, also known as a gyro, allow you to spin your handlebars around without your brake cables getting wrapped up. Gyros can be very overwhelming and complicated to install and get working properly. Here, we discuss how to install your gyro kit and get your brakes working top-notch!</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/gyro-detangler/cp1471</t>
+  </si>
+  <si>
+    <t>BMX Brake Types &amp; FAQ</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/brake_faq/thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Learn all about the different types of brakes used in the BMX world, both freestyle and race. We take a deep dive on brake types, brake cables, removable brake mounts, brake pads, gyros and more.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-brake-types-faq/cp1460</t>
   </si>
 </sst>
 </file>
@@ -506,10 +734,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674831E4-6510-4789-AF71-D3A711C4CE6F}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
@@ -542,13 +770,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>1390</v>
@@ -559,16 +787,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E3">
         <v>1500</v>
@@ -579,16 +807,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="E4">
         <v>1369</v>
@@ -599,16 +827,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>1459</v>
@@ -619,16 +847,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>1308</v>
@@ -637,9 +865,389 @@
         <v>44964</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>1673</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>1185</v>
+      </c>
+      <c r="F8" s="2">
+        <v>44726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>1596</v>
+      </c>
+      <c r="F9" s="2">
+        <v>45656</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>903</v>
+      </c>
+      <c r="F10" s="2">
+        <v>44435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11">
+        <v>485</v>
+      </c>
+      <c r="F11" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12">
+        <v>1362</v>
+      </c>
+      <c r="F12" s="2">
+        <v>45097</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13">
+        <v>907</v>
+      </c>
+      <c r="F13" s="2">
+        <v>44440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>488</v>
+      </c>
+      <c r="F14" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15">
+        <v>1819</v>
+      </c>
+      <c r="F15" s="2">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16">
+        <v>1800</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>1715</v>
+      </c>
+      <c r="F17" s="2">
+        <v>45890</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>1711</v>
+      </c>
+      <c r="F18" s="2">
+        <v>45876</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19">
+        <v>1687</v>
+      </c>
+      <c r="F19" s="2">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20">
+        <v>1662</v>
+      </c>
+      <c r="F20" s="2">
+        <v>45733</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21">
+        <v>1612</v>
+      </c>
+      <c r="F21" s="2">
+        <v>45715</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22">
+        <v>1586</v>
+      </c>
+      <c r="F22" s="2">
+        <v>45633</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23">
+        <v>1572</v>
+      </c>
+      <c r="F23" s="2">
+        <v>45593</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24">
+        <v>1471</v>
+      </c>
+      <c r="F24" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25">
+        <v>1460</v>
+      </c>
+      <c r="F25" s="2">
+        <v>45295</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{32DB9B8C-A366-4C6E-89D0-60B33590E24F}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/sites/danscomp/team_riders/teamriders2025_2.jpg" xr:uid="{32DB9B8C-A366-4C6E-89D0-60B33590E24F}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{563B04B7-F378-49A3-B282-4E12C84BD449}"/>
     <hyperlink ref="D3" r:id="rId3" xr:uid="{94A9F92A-0AC6-4EDA-9CBA-F79A046DC061}"/>
     <hyperlink ref="D4" r:id="rId4" xr:uid="{02449328-A529-4F1A-B5BA-7DF01846F8EF}"/>

--- a/Blog.xlsx
+++ b/Blog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\austinz\Desktop\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A05A778-9597-4A76-AD68-9F9A0B7F1612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7BF211-A600-4724-83FB-0EFE28F1BCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{275F5470-4899-460C-BFB9-CB0C30FDBC08}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{275F5470-4899-460C-BFB9-CB0C30FDBC08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="204">
   <si>
     <t>pageTitle</t>
   </si>
@@ -342,6 +342,312 @@
   </si>
   <si>
     <t>https://www.danscomp.com/bmx-brake-types-faq/cp1460</t>
+  </si>
+  <si>
+    <t>How To Wallride a BMX Bike</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_tricks/wallride.jpg</t>
+  </si>
+  <si>
+    <t>Learn the art of wallriding with our BMX how-to guide! Discover the thrill of riding your bike on vertical surfaces. We provide tips on where to learn, emphasizing the importance of a bank/wedge ramp or a slanted wall for a smoother experience. Check out images illustrating the correct technique.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-wallride-a-bmx-bike/cp1458</t>
+  </si>
+  <si>
+    <t>How To 360 a BMX Bike</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_tricks/360.jpg</t>
+  </si>
+  <si>
+    <t>Learn the art of the BMX 360 with Dan's Comp How-To Series. This guide covers key aspects: versatile 360 variations, ideal learning locations (flat ground, ramps), and personalized spinning directions based on foot positioning. Progress from 180 to 360, mastering techniques like the 360 tail tap. Discover the physics of carving takeoffs for controlled spins and leveling out mid-air for smooth landings. Insightful tips on body positioning and gaze direction enhance the learning process.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-360-a-bmx-bike/cp1457</t>
+  </si>
+  <si>
+    <t>BMX How To Barspin</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_barspin/thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Dive into the thrilling world of BMX tricks with our latest blog! Uncover the secrets to mastering the barspin, a jaw-dropping maneuver that adds style to your ride. From essential tips on bike control to step-by-step guidance, we've got you covered. Join us as we break down the barriers to barspin success, empowering riders of all levels to elevate their skills and leave a lasting impression at the skatepark. Unleash your BMX potential with this must-read guide!</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-how-to-barspin/cp1456</t>
+  </si>
+  <si>
+    <t>How To Air Out of a Quarter Pipe: BMX</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_airout/thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Learning how to air out of a quarter pipe is something that takes your riding to a whole new level. Not only is it fun and looks cool, but it allows you to carry more speed around a skate park and open up a whole new world of lines and tricks. Airing out can certainly be scary but here we break this down in to small steps to help you get comfortable with the feeling of a quarter pipe and work your way up to more and more air.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-air-out-of-a-quarter-pipe-bmx/cp1455</t>
+  </si>
+  <si>
+    <t>How To Tailwhip a BMX Bike</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/how_to_tailwhip/thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>Dan's Comp BMX rider Austin Zentmyer takes you through the steps of learning how to tail whip and provides some very useful tips not found in other how to's.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-tailwhip-a-bmx-bike/cp1454</t>
+  </si>
+  <si>
+    <t>Tech Help: Freecoasters</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/get_tech_freecoaster.jpg</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/tech-help-freecoasters/cp1453</t>
+  </si>
+  <si>
+    <t>Freecoaseters very well may be just as common as a cassette hub these days. While they make a lot of tricks much easier, they can be very confusing to understand and work on. Here, we break down the different types of freecoasters as well as how to perform maintenance on them to keep the working properly.</t>
+  </si>
+  <si>
+    <t>Boston Jam Video &amp; Photos</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/boston_jam/after/dsc08942.jpg</t>
+  </si>
+  <si>
+    <t>The BMX scene is alive and well in the Northeast! Dan's Comp put on a jam at the incredible The Edge Indoor Skatepark and brought out a bunch of our team riders to have fun and shred with the super rad locals there in the Boston area. Dan's pro riders Matt Ray and Joe Battaglia were both there throwing down some hammers. Brant Moore was on the scene to capture all the fun and radness that went down.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/boston-jam-video-photos/cp1449</t>
+  </si>
+  <si>
+    <t>Planetary Freecoasters: The Future of Freecoasters?</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/aksptulIkPM/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Planetary freecoaster wheels like the BSD Revolution, Colony Swarm and Alienation Venus have become increasingly popular as of late. But will this all-new design take over the freecoaster market? We'll let you be the judge as we review the pros and cons of the planetary freecoaster system. These hubs could likely be the future of BMX freecoasters.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/planetary-freecoasters-the-future-of-freecoasters/cp1166</t>
+  </si>
+  <si>
+    <t>Skatepark Etiquette</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/x51VqMX4xss/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>We've all been there. You're out riding the local park and one of THESE characters show up and ruin it for everyone. Don't get discouraged. Sometimes people are unaware of proper skatepark etiquette and it's our job to teach them these unwritten rules.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/skatepark-etiquette/cp1093</t>
+  </si>
+  <si>
+    <t>How To Turndown</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/Yt9rp2L1dEM/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>A true BMX classic! The Turndown remains one of the most popular and stylish tricks to date and has become a mainstay in the BMX community. Every rider has their own unique style, and the Turndown really highlights those individual characteristics.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-turndown/cp1086</t>
+  </si>
+  <si>
+    <t>How To Manual A Bike</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/rwSUPtH5BFg/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Manuals are one of those fundamental BMX tricks that every rider should try to learn. Not only are manuals extremely fun, but they open up a ton of other trick possibilities. We break down proper manual technique including the proper way to pull up, balance and turn. These tips and techniques are not regulated to just BMX. The same principles can be applied to cruisers, dirt jump bikes, mountain bikes, Bike Life bikes and so on.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/how-to-manual-a-bike/cp901</t>
+  </si>
+  <si>
+    <t>S&amp;M Rail Slide Pipe Review</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/qZ5uQI7zA8s/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>The crew over at S&amp;M Bikes has overhauled and relaunched their portable grind rail lineup. The S&amp;M Slide Pipe V2 is available in both fixed height or adjustable, and built to handle some heavy grind sessions. Could the Slide Pipe be the best portable grind rail? Mike gives you his overall impressions with the help of some friends.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/s-m-rail-slide-pipe-review/cp878</t>
+  </si>
+  <si>
+    <t>Top 5 Parts That Changed BMX Forever</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/ipvTOpOghPQ/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>New parts in BMX come and go, fads change and technology changes, but some things are here to stay. Long time Dan's Comp employee/rider, Mike, gives you his Top 5 game changing BMX parts.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/top-5-parts-that-changed-bmx-forever/cp866</t>
+  </si>
+  <si>
+    <t>BMX Wheel &amp; Hub: Answering All Your Questions</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/bmx/tech-help/img/4_cross_wheel.jpg</t>
+  </si>
+  <si>
+    <t>Here, we go deep, I mean deep, in depth on all the questions we et asked about BMX wheels and hubs. This can be a very confusing topic, considering all the different hub types, bearings, axles, spokes, nipples, lacing patterns, and so much more. Class is in session!</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-wheel-hub-answering-all-your-questions/cp501</t>
+  </si>
+  <si>
+    <t>BMX Tire Installation Instructions</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/UuyKUpoCOjs/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Instructions and full video guide on how to install your BMX tube and tire. Also, learn what size tires will fit on your bike.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-tire-installation-instructions/cp500</t>
+  </si>
+  <si>
+    <t>BMX Stem Sizes &amp; Install</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/bmx/tech-help/img/stem_length.jpg</t>
+  </si>
+  <si>
+    <t>This webpage serves as a comprehensive guide to BMX stem sizing, compatibility, and selection, tailored for both freestyle and racing disciplines. It breaks down the three major considerations when choosing a stem: steerer tube size, handlebar clamp diameter, and stem length/reach. The content explains the difference between front load and top load stems, including how they affect bar height and riding position through rise and stack height measurements.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-stem-sizes-install/cp499</t>
+  </si>
+  <si>
+    <t>BMX Sprocket FAQ's</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/sprocket.jpg</t>
+  </si>
+  <si>
+    <t>How do I know which sprocket will work with my bike? What is the difference between Bolt Drive, Spline Drive, and Socket Drive Sprockets? What is meant by gear ratio? How do I determine what gear ratio is best for me? Learn all this and more here at Dan's Comp.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-sprocket-faqs/cp498</t>
+  </si>
+  <si>
+    <t>BMX Seat Install: How To</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/k8fPbeIqyqA/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>There's several different types of BMX seats out there these days and a lot of confusing terms. What is a pivotal seat? A railed seat sounds uncomfortable, who would want that? Stealth mount or traditional? I don't know! Learn all about the different types and terms for BMX seats here.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-seat-install-how-to/cp497</t>
+  </si>
+  <si>
+    <t>BMX Pedal Install: How To</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/RdMBfOnI594/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Pedals are a part of the bike that seem pretty basic, however, there's so many different types. They can also be very tricky to install and remove considering one of the pedals has reverse threads. Righty-tighty lefty-loosey? Nuh-uh! Dan's Comp gives you a full breakdown on all the different types of pedals and some tips on how to install them.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-pedal-install-how-to/cp494</t>
+  </si>
+  <si>
+    <t>BMX Headset Types &amp; Installation Instructions</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/headset1.jpg</t>
+  </si>
+  <si>
+    <t>Learn all about the various different types of headsets in both freestyle and race BMX and how to install them. Does your headset have play in it? Does it creak or not spin properly? Here are some installation tips and tricks on how to install and maintain you BMX headset whether it's integrated or standard.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-headset-types-installation-instructions/cp492</t>
+  </si>
+  <si>
+    <t>BMX Handlebar FAQ &amp; Installation Instructions</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/i2fJCIgLUcY/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Here, we breakdown what to look for when buying a new handlebar as well as a guide on how to properly install them. Installing your bars incorrectly could throw off how the entire bike handles and could lead to the bars moving and causing you to crash.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-handlebar-faq-installation-instructions/cp491</t>
+  </si>
+  <si>
+    <t>BMX Grip Install: How To</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/tHYzw8V3tuM/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>Putting new grips on your BMX bike can be one of the most frustrating things to do. That is, unless you know the pro tips. Here, we explain different ways to install your BMX grips to make it a quick and easy process</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-grip-install-how-to/cp489</t>
+  </si>
+  <si>
+    <t>BMX Fork: Everything to Know</t>
+  </si>
+  <si>
+    <t>https://img.youtube.com/vi/Vn-PnxH_mto/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>BMX forks have a lot of factors that often get overlooked by most riders. Here, we explain those factors, including fork height, offset, steer tube length, bearing race and more. We also explain how to properly install you fork.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-fork-everything-to-know/cp487</t>
+  </si>
+  <si>
+    <t>BMX Chain Install: How To</t>
+  </si>
+  <si>
+    <t>We explain how to use the proper tools to install your chain on your BMX bike. We also discuss the different width of BMX chains available.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-chain-install-how-to/cp484</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/bmx/tech-help/img/mid_bb.jpg</t>
+  </si>
+  <si>
+    <t>BMX Bottom Bracket Types</t>
+  </si>
+  <si>
+    <t>There are a handful of different bottom bracket types in the BMX world. Understanding these different types is very important when purchasing a new bottom bracket kit, frame, and/or cranks.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-bottom-bracket-types/cp481</t>
+  </si>
+  <si>
+    <t>BMX Crank Length Sizing Chart</t>
+  </si>
+  <si>
+    <t>The length of your crank arm is an important factor to consider for both BMX racing and freestyle. Here, we show how this is measured and take a look at recommended crank arm sizing based on a riders height.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/bmx-crank-length-sizing-chart/cp479</t>
   </si>
 </sst>
 </file>
@@ -734,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674831E4-6510-4789-AF71-D3A711C4CE6F}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -1245,6 +1551,526 @@
         <v>45295</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26">
+        <v>1458</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45289</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27">
+        <v>1457</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28">
+        <v>1456</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29">
+        <v>1455</v>
+      </c>
+      <c r="F29" s="2">
+        <v>45286</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30">
+        <v>1454</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31">
+        <v>1453</v>
+      </c>
+      <c r="F31" s="2">
+        <v>45282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32">
+        <v>1449</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45271</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33">
+        <v>1166</v>
+      </c>
+      <c r="F33" s="2">
+        <v>44690</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34">
+        <v>1093</v>
+      </c>
+      <c r="F34" s="2">
+        <v>44572</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35">
+        <v>1086</v>
+      </c>
+      <c r="F35" s="2">
+        <v>44566</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36">
+        <v>901</v>
+      </c>
+      <c r="F36" s="2">
+        <v>44432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37">
+        <v>878</v>
+      </c>
+      <c r="F37" s="2">
+        <v>44406</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38">
+        <v>866</v>
+      </c>
+      <c r="F38" s="2">
+        <v>44392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39">
+        <v>501</v>
+      </c>
+      <c r="F39" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40">
+        <v>500</v>
+      </c>
+      <c r="F40" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41">
+        <v>499</v>
+      </c>
+      <c r="F41" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" t="s">
+        <v>169</v>
+      </c>
+      <c r="E42">
+        <v>498</v>
+      </c>
+      <c r="F42" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43">
+        <v>497</v>
+      </c>
+      <c r="F43" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44">
+        <v>494</v>
+      </c>
+      <c r="F44" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" t="s">
+        <v>179</v>
+      </c>
+      <c r="C45" t="s">
+        <v>180</v>
+      </c>
+      <c r="D45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45">
+        <v>492</v>
+      </c>
+      <c r="F45" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46">
+        <v>491</v>
+      </c>
+      <c r="F46" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>186</v>
+      </c>
+      <c r="B47" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" t="s">
+        <v>188</v>
+      </c>
+      <c r="D47" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47">
+        <v>489</v>
+      </c>
+      <c r="F47" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>190</v>
+      </c>
+      <c r="B48" t="s">
+        <v>191</v>
+      </c>
+      <c r="C48" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48">
+        <v>487</v>
+      </c>
+      <c r="F48" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" t="s">
+        <v>196</v>
+      </c>
+      <c r="E49">
+        <v>484</v>
+      </c>
+      <c r="F49" s="2">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" t="s">
+        <v>200</v>
+      </c>
+      <c r="E50">
+        <v>481</v>
+      </c>
+      <c r="F50" s="2">
+        <v>43755</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" t="s">
+        <v>202</v>
+      </c>
+      <c r="D51" t="s">
+        <v>203</v>
+      </c>
+      <c r="E51">
+        <v>479</v>
+      </c>
+      <c r="F51" s="2">
+        <v>43755</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/sites/danscomp/team_riders/teamriders2025_2.jpg" xr:uid="{32DB9B8C-A366-4C6E-89D0-60B33590E24F}"/>

--- a/Blog.xlsx
+++ b/Blog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\austinz\Desktop\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7BF211-A600-4724-83FB-0EFE28F1BCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD83553-44F3-4C34-A052-EAB894825BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{275F5470-4899-460C-BFB9-CB0C30FDBC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{275F5470-4899-460C-BFB9-CB0C30FDBC08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="208">
   <si>
     <t>pageTitle</t>
   </si>
@@ -221,9 +221,6 @@
     <t>https://img.youtube.com/vi/yi_QlPDaUKc/maxresdefault.jpg</t>
   </si>
   <si>
-    <t>How-To Tuck No Hander | Featuring Brady Baker</t>
-  </si>
-  <si>
     <t>https://www.danscomp.com/40th-anniversary-about-us/cp1800</t>
   </si>
   <si>
@@ -648,6 +645,21 @@
   </si>
   <si>
     <t>https://www.danscomp.com/bmx-crank-length-sizing-chart/cp479</t>
+  </si>
+  <si>
+    <t>Spoke Calculator</t>
+  </si>
+  <si>
+    <t>https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/contentpages/danscomp/tech_help/spoke_calculator.jpg</t>
+  </si>
+  <si>
+    <t>Master your next wheel build with the Dan's Comp Spoke Calculator. Whether you’re lacing a custom wheel or replacing some broken spokes, getting the perfect spoke length is critical for a high-tension, wobble-free ride.</t>
+  </si>
+  <si>
+    <t>https://www.danscomp.com/spoke-calculator/cp1810</t>
+  </si>
+  <si>
+    <t>How To Tuck No Hander | Featuring Brady Baker</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674831E4-6510-4789-AF71-D3A711C4CE6F}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -1113,82 +1125,82 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>1369</v>
+        <v>1673</v>
       </c>
       <c r="F4" s="2">
-        <v>45106</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>1459</v>
+        <v>1369</v>
       </c>
       <c r="F5" s="2">
-        <v>45293</v>
+        <v>45106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>1308</v>
+        <v>1459</v>
       </c>
       <c r="F6" s="2">
-        <v>44964</v>
+        <v>45293</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>1673</v>
+        <v>1308</v>
       </c>
       <c r="F7" s="2">
-        <v>45755</v>
+        <v>44964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1213,176 +1225,176 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E9">
-        <v>1596</v>
+        <v>485</v>
       </c>
       <c r="F9" s="2">
-        <v>45656</v>
+        <v>43756</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E10">
-        <v>903</v>
+        <v>1362</v>
       </c>
       <c r="F10" s="2">
-        <v>44435</v>
+        <v>45097</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E11">
-        <v>485</v>
+        <v>907</v>
       </c>
       <c r="F11" s="2">
-        <v>43756</v>
+        <v>44440</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>1362</v>
+        <v>1596</v>
       </c>
       <c r="F12" s="2">
-        <v>45097</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E13">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="F13" s="2">
-        <v>44440</v>
+        <v>44435</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E14">
-        <v>488</v>
+        <v>1800</v>
       </c>
       <c r="F14" s="2">
-        <v>43756</v>
+        <v>46049</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E15">
-        <v>1819</v>
+        <v>488</v>
       </c>
       <c r="F15" s="2">
-        <v>46076</v>
+        <v>43756</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>207</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E16">
-        <v>1800</v>
+        <v>1819</v>
       </c>
       <c r="F16" s="2">
-        <v>46049</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17">
         <v>1715</v>
@@ -1393,16 +1405,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>1711</v>
@@ -1413,16 +1425,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19">
         <v>1687</v>
@@ -1433,16 +1445,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
         <v>78</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>79</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
       </c>
       <c r="E20">
         <v>1662</v>
@@ -1453,16 +1465,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>1612</v>
@@ -1473,16 +1485,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
         <v>86</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
         <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" t="s">
-        <v>88</v>
       </c>
       <c r="E22">
         <v>1586</v>
@@ -1493,16 +1505,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
         <v>90</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>91</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
       </c>
       <c r="E23">
         <v>1572</v>
@@ -1513,16 +1525,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
         <v>95</v>
       </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>97</v>
       </c>
       <c r="E24">
         <v>1471</v>
@@ -1533,16 +1545,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
         <v>98</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>99</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
       </c>
       <c r="E25">
         <v>1460</v>
@@ -1553,16 +1565,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
         <v>102</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>103</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
       </c>
       <c r="E26">
         <v>1458</v>
@@ -1573,16 +1585,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
         <v>106</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>107</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>109</v>
       </c>
       <c r="E27">
         <v>1457</v>
@@ -1593,16 +1605,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
         <v>110</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>111</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
       </c>
       <c r="E28">
         <v>1456</v>
@@ -1613,16 +1625,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
         <v>114</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>115</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
       </c>
       <c r="E29">
         <v>1455</v>
@@ -1633,16 +1645,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
         <v>118</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>119</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
       </c>
       <c r="E30">
         <v>1454</v>
@@ -1653,16 +1665,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" t="s">
         <v>122</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" t="s">
         <v>123</v>
-      </c>
-      <c r="C31" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" t="s">
-        <v>124</v>
       </c>
       <c r="E31">
         <v>1453</v>
@@ -1673,16 +1685,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" t="s">
         <v>126</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>127</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>129</v>
       </c>
       <c r="E32">
         <v>1449</v>
@@ -1693,16 +1705,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
         <v>130</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>131</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>132</v>
-      </c>
-      <c r="D33" t="s">
-        <v>133</v>
       </c>
       <c r="E33">
         <v>1166</v>
@@ -1713,16 +1725,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" t="s">
         <v>134</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>135</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>136</v>
-      </c>
-      <c r="D34" t="s">
-        <v>137</v>
       </c>
       <c r="E34">
         <v>1093</v>
@@ -1733,16 +1745,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" t="s">
         <v>138</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>139</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>140</v>
-      </c>
-      <c r="D35" t="s">
-        <v>141</v>
       </c>
       <c r="E35">
         <v>1086</v>
@@ -1753,16 +1765,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" t="s">
         <v>142</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>143</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>144</v>
-      </c>
-      <c r="D36" t="s">
-        <v>145</v>
       </c>
       <c r="E36">
         <v>901</v>
@@ -1773,16 +1785,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="s">
         <v>146</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>147</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>148</v>
-      </c>
-      <c r="D37" t="s">
-        <v>149</v>
       </c>
       <c r="E37">
         <v>878</v>
@@ -1793,16 +1805,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" t="s">
         <v>150</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>151</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>152</v>
-      </c>
-      <c r="D38" t="s">
-        <v>153</v>
       </c>
       <c r="E38">
         <v>866</v>
@@ -1813,16 +1825,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" t="s">
         <v>154</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>155</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>156</v>
-      </c>
-      <c r="D39" t="s">
-        <v>157</v>
       </c>
       <c r="E39">
         <v>501</v>
@@ -1833,16 +1845,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" t="s">
         <v>158</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>159</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>160</v>
-      </c>
-      <c r="D40" t="s">
-        <v>161</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -1853,16 +1865,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" t="s">
         <v>162</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>163</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>164</v>
-      </c>
-      <c r="D41" t="s">
-        <v>165</v>
       </c>
       <c r="E41">
         <v>499</v>
@@ -1873,16 +1885,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" t="s">
         <v>166</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>167</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>168</v>
-      </c>
-      <c r="D42" t="s">
-        <v>169</v>
       </c>
       <c r="E42">
         <v>498</v>
@@ -1893,16 +1905,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" t="s">
         <v>170</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>171</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>172</v>
-      </c>
-      <c r="D43" t="s">
-        <v>173</v>
       </c>
       <c r="E43">
         <v>497</v>
@@ -1913,16 +1925,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" t="s">
         <v>174</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>175</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>176</v>
-      </c>
-      <c r="D44" t="s">
-        <v>177</v>
       </c>
       <c r="E44">
         <v>494</v>
@@ -1933,16 +1945,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" t="s">
         <v>178</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>179</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>180</v>
-      </c>
-      <c r="D45" t="s">
-        <v>181</v>
       </c>
       <c r="E45">
         <v>492</v>
@@ -1953,16 +1965,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" t="s">
         <v>182</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>183</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>184</v>
-      </c>
-      <c r="D46" t="s">
-        <v>185</v>
       </c>
       <c r="E46">
         <v>491</v>
@@ -1973,16 +1985,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" t="s">
         <v>186</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>187</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>188</v>
-      </c>
-      <c r="D47" t="s">
-        <v>189</v>
       </c>
       <c r="E47">
         <v>489</v>
@@ -1993,16 +2005,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" t="s">
         <v>190</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>191</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>192</v>
-      </c>
-      <c r="D48" t="s">
-        <v>193</v>
       </c>
       <c r="E48">
         <v>487</v>
@@ -2013,16 +2025,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" t="s">
         <v>194</v>
       </c>
-      <c r="B49" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>195</v>
-      </c>
-      <c r="D49" t="s">
-        <v>196</v>
       </c>
       <c r="E49">
         <v>484</v>
@@ -2033,16 +2045,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" t="s">
         <v>198</v>
       </c>
-      <c r="B50" t="s">
-        <v>197</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>199</v>
-      </c>
-      <c r="D50" t="s">
-        <v>200</v>
       </c>
       <c r="E50">
         <v>481</v>
@@ -2053,22 +2065,42 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>200</v>
+      </c>
+      <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" t="s">
         <v>201</v>
       </c>
-      <c r="B51" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>202</v>
-      </c>
-      <c r="D51" t="s">
-        <v>203</v>
       </c>
       <c r="E51">
         <v>479</v>
       </c>
       <c r="F51" s="2">
         <v>43755</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" t="s">
+        <v>204</v>
+      </c>
+      <c r="C52" t="s">
+        <v>205</v>
+      </c>
+      <c r="D52" t="s">
+        <v>206</v>
+      </c>
+      <c r="E52">
+        <v>1810</v>
+      </c>
+      <c r="F52" s="2">
+        <v>46062</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2108,7 @@
     <hyperlink ref="B2" r:id="rId1" display="https://images.danscomp.com/cdn-cgi/image/f=auto,width=400/images/sites/danscomp/team_riders/teamriders2025_2.jpg" xr:uid="{32DB9B8C-A366-4C6E-89D0-60B33590E24F}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{563B04B7-F378-49A3-B282-4E12C84BD449}"/>
     <hyperlink ref="D3" r:id="rId3" xr:uid="{94A9F92A-0AC6-4EDA-9CBA-F79A046DC061}"/>
-    <hyperlink ref="D4" r:id="rId4" xr:uid="{02449328-A529-4F1A-B5BA-7DF01846F8EF}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{02449328-A529-4F1A-B5BA-7DF01846F8EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
